--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -814,8 +814,7 @@
 </t>
   </si>
   <si>
-    <t>Observationのためのビジネス識別子  
-【JP Core仕様】当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。</t>
+    <t>Observationのためのビジネス識別子 【JP Core仕様】当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。</t>
   </si>
   <si>
     <t>例：実施日に連番を付加した番号</t>
@@ -934,16 +933,15 @@
     <t>3</t>
   </si>
   <si>
-    <t>Observationの種類（タイプ）の分類
-【JP Core仕様】以下を指定する。
+    <t>Observationの種類（タイプ）の分類</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】以下を指定する。
 第1コード：exam
 第2コード：LP89803-8 （Dental）
 第3コード：DO-1-01 （ToothExistence）</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
-  </si>
-  <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
@@ -1057,6 +1055,9 @@
   </si>
   <si>
     <t>第2カテゴリはLOINCのコードLP89803-8固定で必須とする、ValueSetは指定しない</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -7477,7 +7478,7 @@
         <v>335</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>298</v>
@@ -7564,7 +7565,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>310</v>
@@ -7682,7 +7683,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>312</v>
@@ -7802,7 +7803,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>314</v>
@@ -7924,7 +7925,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>316</v>
@@ -8042,7 +8043,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>318</v>
@@ -8162,7 +8163,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>320</v>
@@ -8207,7 +8208,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>83</v>
@@ -8284,7 +8285,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>323</v>
@@ -8404,7 +8405,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>325</v>
@@ -8447,7 +8448,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>83</v>
@@ -8524,7 +8525,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>328</v>
@@ -8644,7 +8645,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>330</v>
@@ -8766,7 +8767,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>332</v>
@@ -8888,13 +8889,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>294</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>83</v>
@@ -8919,13 +8920,13 @@
         <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>298</v>
@@ -8957,7 +8958,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -9010,7 +9011,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>310</v>
@@ -9128,7 +9129,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>312</v>
@@ -9248,7 +9249,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>314</v>
@@ -9370,7 +9371,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>316</v>
@@ -9488,7 +9489,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>318</v>
@@ -9608,7 +9609,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>320</v>
@@ -9653,7 +9654,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>83</v>
@@ -9730,7 +9731,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>323</v>
@@ -9850,7 +9851,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>325</v>
@@ -9893,7 +9894,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>83</v>
@@ -9970,7 +9971,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>328</v>
@@ -10090,7 +10091,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>330</v>
@@ -10212,7 +10213,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>332</v>
@@ -10334,14 +10335,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10363,16 +10364,16 @@
         <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10397,13 +10398,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10421,7 +10422,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10436,30 +10437,30 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10574,10 +10575,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10694,10 +10695,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10723,10 +10724,10 @@
         <v>186</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>189</v>
@@ -10816,10 +10817,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10934,10 +10935,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11054,10 +11055,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11099,7 +11100,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>83</v>
@@ -11176,10 +11177,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11296,10 +11297,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11339,7 +11340,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>83</v>
@@ -11416,10 +11417,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11462,7 +11463,7 @@
         <v>83</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>83</v>
@@ -11536,10 +11537,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11658,10 +11659,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11780,10 +11781,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11806,19 +11807,19 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -11867,7 +11868,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11882,19 +11883,19 @@
         <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
@@ -11902,10 +11903,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11928,16 +11929,16 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11987,7 +11988,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12008,13 +12009,13 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12022,14 +12023,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12048,19 +12049,19 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12109,7 +12110,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12124,19 +12125,19 @@
         <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12144,14 +12145,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12170,19 +12171,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12231,7 +12232,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12246,19 +12247,19 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12266,10 +12267,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12292,16 +12293,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12351,7 +12352,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12372,13 +12373,13 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12386,10 +12387,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12412,19 +12413,19 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12473,7 +12474,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12488,19 +12489,19 @@
         <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -12508,10 +12509,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12537,16 +12538,16 @@
         <v>171</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12571,11 +12572,11 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>286</v>
+        <v>118</v>
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -12593,7 +12594,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12602,7 +12603,7 @@
         <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>106</v>
@@ -12611,27 +12612,27 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12657,16 +12658,16 @@
         <v>171</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12691,13 +12692,13 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -12715,7 +12716,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12724,7 +12725,7 @@
         <v>94</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>106</v>
@@ -12739,7 +12740,7 @@
         <v>137</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12750,14 +12751,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12779,16 +12780,16 @@
         <v>171</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -12813,13 +12814,13 @@
         <v>83</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -12837,7 +12838,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12855,27 +12856,27 @@
         <v>83</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12898,19 +12899,19 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -12959,7 +12960,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12980,10 +12981,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12994,10 +12995,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13023,13 +13024,13 @@
         <v>171</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13059,7 +13060,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13077,7 +13078,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13095,27 +13096,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13141,16 +13142,16 @@
         <v>171</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13175,13 +13176,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13199,7 +13200,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13220,10 +13221,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13234,10 +13235,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13260,16 +13261,16 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13319,7 +13320,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13337,27 +13338,27 @@
         <v>83</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13380,16 +13381,16 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13439,7 +13440,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13457,27 +13458,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13500,19 +13501,19 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13561,7 +13562,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13573,7 +13574,7 @@
         <v>83</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>83</v>
@@ -13582,10 +13583,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13596,10 +13597,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13714,10 +13715,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13834,14 +13835,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13863,10 +13864,10 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>183</v>
@@ -13921,7 +13922,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13956,10 +13957,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13982,13 +13983,13 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14039,7 +14040,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14048,7 +14049,7 @@
         <v>94</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>106</v>
@@ -14060,10 +14061,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14074,10 +14075,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14100,13 +14101,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14157,7 +14158,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14166,7 +14167,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14178,10 +14179,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14192,10 +14193,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14221,16 +14222,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14258,10 +14259,10 @@
         <v>118</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14279,7 +14280,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14297,13 +14298,13 @@
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14314,10 +14315,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14343,16 +14344,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14377,13 +14378,13 @@
         <v>83</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14401,7 +14402,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14419,13 +14420,13 @@
         <v>83</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14436,10 +14437,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14462,17 +14463,17 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14521,7 +14522,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14545,7 +14546,7 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14556,10 +14557,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14585,10 +14586,10 @@
         <v>153</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14639,7 +14640,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14660,10 +14661,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14674,10 +14675,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14700,16 +14701,16 @@
         <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14759,7 +14760,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14780,10 +14781,10 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14794,10 +14795,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14820,16 +14821,16 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14879,7 +14880,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14900,10 +14901,10 @@
         <v>83</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14914,10 +14915,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14940,19 +14941,19 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15001,7 +15002,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15022,10 +15023,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15036,10 +15037,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15154,10 +15155,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15274,14 +15275,14 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15303,10 +15304,10 @@
         <v>139</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>183</v>
@@ -15361,7 +15362,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15396,10 +15397,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15425,16 +15426,16 @@
         <v>171</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15459,13 +15460,13 @@
         <v>83</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -15483,7 +15484,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>94</v>
@@ -15501,16 +15502,16 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -15518,10 +15519,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15544,19 +15545,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15605,7 +15606,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15623,27 +15624,27 @@
         <v>83</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15669,16 +15670,16 @@
         <v>171</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -15703,13 +15704,13 @@
         <v>83</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -15727,7 +15728,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15736,7 +15737,7 @@
         <v>94</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>106</v>
@@ -15751,7 +15752,7 @@
         <v>137</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15762,14 +15763,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15791,16 +15792,16 @@
         <v>171</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -15825,13 +15826,13 @@
         <v>83</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -15849,7 +15850,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15867,27 +15868,27 @@
         <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15913,16 +15914,16 @@
         <v>84</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -15971,7 +15972,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15992,10 +15993,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -846,8 +846,7 @@
 </t>
   </si>
   <si>
-    <t>実施されるプラン、提案、依頼  
-【JP Core仕様】未使用</t>
+    <t>実施されるプラン、提案、依頼 【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>本プロファイル（特定の歯の有無・状態）は口腔診査レポートに紐付く前提のため、本プロファイル特有の定義はしない。</t>
